--- a/docs/downloads/04/tbl_origine_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/04/tbl_origine_alaotra_ambohidrony.xlsx
@@ -443,12 +443,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>5.8</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -535,12 +529,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>11.1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -557,12 +545,6 @@
         <is>
           <t>Zana-tany</t>
         </is>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>11.1</v>
       </c>
     </row>
     <row r="10">
